--- a/survey_templates/032_public_dietary_habits_questionnaire--survey_templates.xlsx
+++ b/survey_templates/032_public_dietary_habits_questionnaire--survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1102,8 +1102,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="33" customWidth="1" min="1" max="1"/>
-    <col width="47" customWidth="1" min="2" max="2"/>
-    <col width="47" customWidth="1" min="3" max="3"/>
+    <col width="25" customWidth="1" min="2" max="2"/>
+    <col width="25" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'one'}</t>
+          <t>one</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'One'}</t>
+          <t>One</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'two'}</t>
+          <t>two</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Two'}</t>
+          <t>Two</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'three_or_more'}</t>
+          <t>three_or_more</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Three or more'}</t>
+          <t>Three or more</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'male'}</t>
+          <t>male</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Male'}</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'female'}</t>
+          <t>female</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Female'}</t>
+          <t>Female</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'other_(please_specify)'}</t>
+          <t>other_(please_specify)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Other (please specify)'}</t>
+          <t>Other (please specify)</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'do_not_wish_to_answer'}</t>
+          <t>do_not_wish_to_answer</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Do not wish to answer'}</t>
+          <t>Do not wish to answer</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1250,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_'prefer_not_to_say'}</t>
+          <t>prefer_not_to_say</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': 'Prefer not to say'}</t>
+          <t>Prefer not to say</t>
         </is>
       </c>
     </row>
@@ -1267,12 +1267,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'feet_and_inches'}</t>
+          <t>feet_and_inches</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Feet and Inches'}</t>
+          <t>Feet and Inches</t>
         </is>
       </c>
     </row>
@@ -1284,12 +1284,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'centimeters'}</t>
+          <t>centimeters</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Centimeters'}</t>
+          <t>Centimeters</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'other_(please_specify)'}</t>
+          <t>other_(please_specify)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Other (please specify)'}</t>
+          <t>Other (please specify)</t>
         </is>
       </c>
     </row>
@@ -1318,12 +1318,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'not_applicable'}</t>
+          <t>not_applicable</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Not applicable'}</t>
+          <t>Not applicable</t>
         </is>
       </c>
     </row>
@@ -1335,12 +1335,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'daily'}</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Daily'}</t>
+          <t>Daily</t>
         </is>
       </c>
     </row>
@@ -1352,12 +1352,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'weekly'}</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Weekly'}</t>
+          <t>Weekly</t>
         </is>
       </c>
     </row>
@@ -1369,12 +1369,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'monthly'}</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Monthly'}</t>
+          <t>Monthly</t>
         </is>
       </c>
     </row>
@@ -1386,12 +1386,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'rarely'}</t>
+          <t>rarely</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Rarely'}</t>
+          <t>Rarely</t>
         </is>
       </c>
     </row>
@@ -1403,12 +1403,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'breakfast'}</t>
+          <t>breakfast</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Breakfast'}</t>
+          <t>Breakfast</t>
         </is>
       </c>
     </row>
@@ -1420,12 +1420,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'lunch'}</t>
+          <t>lunch</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Lunch'}</t>
+          <t>Lunch</t>
         </is>
       </c>
     </row>
@@ -1437,12 +1437,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'dinner'}</t>
+          <t>dinner</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Dinner'}</t>
+          <t>Dinner</t>
         </is>
       </c>
     </row>
@@ -1454,12 +1454,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'early'}</t>
+          <t>early</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Early'}</t>
+          <t>Early</t>
         </is>
       </c>
     </row>
@@ -1471,12 +1471,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'late'}</t>
+          <t>late</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Late'}</t>
+          <t>Late</t>
         </is>
       </c>
     </row>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'no_set_time'}</t>
+          <t>no_set_time</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'No set time'}</t>
+          <t>No set time</t>
         </is>
       </c>
     </row>
@@ -1505,12 +1505,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'other_(please_specify)'}</t>
+          <t>other_(please_specify)</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Other (please specify)'}</t>
+          <t>Other (please specify)</t>
         </is>
       </c>
     </row>
@@ -1522,12 +1522,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'morning'}</t>
+          <t>morning</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Morning'}</t>
+          <t>Morning</t>
         </is>
       </c>
     </row>
@@ -1539,12 +1539,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'late'}</t>
+          <t>late</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Late'}</t>
+          <t>Late</t>
         </is>
       </c>
     </row>
@@ -1556,12 +1556,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'no_set_time'}</t>
+          <t>no_set_time</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'No set time'}</t>
+          <t>No set time</t>
         </is>
       </c>
     </row>
@@ -1573,12 +1573,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'other_(please_specify)'}</t>
+          <t>other_(please_specify)</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Other (please specify)'}</t>
+          <t>Other (please specify)</t>
         </is>
       </c>
     </row>
@@ -1590,12 +1590,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'early'}</t>
+          <t>early</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Early'}</t>
+          <t>Early</t>
         </is>
       </c>
     </row>
@@ -1607,12 +1607,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'late'}</t>
+          <t>late</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Late'}</t>
+          <t>Late</t>
         </is>
       </c>
     </row>
@@ -1624,12 +1624,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'no_set_time'}</t>
+          <t>no_set_time</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'No set time'}</t>
+          <t>No set time</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'other_(please_specify)'}</t>
+          <t>other_(please_specify)</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Other (please specify)'}</t>
+          <t>Other (please specify)</t>
         </is>
       </c>
     </row>
@@ -1658,12 +1658,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'less_than_3_times_a_day'}</t>
+          <t>less_than_3_times_a_day</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Less than 3 times a day'}</t>
+          <t>Less than 3 times a day</t>
         </is>
       </c>
     </row>
@@ -1675,12 +1675,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'3_or_4_times_a_day'}</t>
+          <t>3_or_4_times_a_day</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': '3 or 4 times a day'}</t>
+          <t>3 or 4 times a day</t>
         </is>
       </c>
     </row>
@@ -1692,12 +1692,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'more_than_5_times_a_day'}</t>
+          <t>more_than_5_times_a_day</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'More than 5 times a day'}</t>
+          <t>More than 5 times a day</t>
         </is>
       </c>
     </row>
@@ -1709,12 +1709,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'morning'}</t>
+          <t>morning</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Morning'}</t>
+          <t>Morning</t>
         </is>
       </c>
     </row>
@@ -1726,12 +1726,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'afternoon'}</t>
+          <t>afternoon</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Afternoon'}</t>
+          <t>Afternoon</t>
         </is>
       </c>
     </row>
@@ -1743,12 +1743,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'evening'}</t>
+          <t>evening</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Evening'}</t>
+          <t>Evening</t>
         </is>
       </c>
     </row>
@@ -1760,12 +1760,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'between_meals'}</t>
+          <t>between_meals</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Between meals'}</t>
+          <t>Between meals</t>
         </is>
       </c>
     </row>
@@ -1777,12 +1777,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'morning'}</t>
+          <t>morning</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Morning'}</t>
+          <t>Morning</t>
         </is>
       </c>
     </row>
@@ -1794,12 +1794,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'afternoon'}</t>
+          <t>afternoon</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Afternoon'}</t>
+          <t>Afternoon</t>
         </is>
       </c>
     </row>
@@ -1811,12 +1811,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'evening'}</t>
+          <t>evening</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Evening'}</t>
+          <t>Evening</t>
         </is>
       </c>
     </row>
@@ -1828,12 +1828,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'1-2_times_a_day'}</t>
+          <t>1-2_times_a_day</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': '1-2 times a day'}</t>
+          <t>1-2 times a day</t>
         </is>
       </c>
     </row>
@@ -1845,12 +1845,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'3-4_times_a_day'}</t>
+          <t>3-4_times_a_day</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': '3-4 times a day'}</t>
+          <t>3-4 times a day</t>
         </is>
       </c>
     </row>
@@ -1862,12 +1862,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'5_or_more_times_a_day'}</t>
+          <t>5_or_more_times_a_day</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': '5 or more times a day'}</t>
+          <t>5 or more times a day</t>
         </is>
       </c>
     </row>
